--- a/studySpecific/ENSEMBLE/20_Doc/詳細設計書_CombineProcess.xlsx
+++ b/studySpecific/ENSEMBLE/20_Doc/詳細設計書_CombineProcess.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Local\iTMS\SDTM_ENSEMBLE\studySpecific\ENSEMBLE\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\張泊江\workshop\ENSEMBLE\SDTM_ENSEMBLE\studySpecific\ENSEMBLE\20_Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B09ABB-6F79-4A87-A807-A4F91244C261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1316,24 +1316,24 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2531,13 +2531,13 @@
       <c r="A50" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="B50" s="57"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="52" t="s">
+      <c r="A52" s="54" t="s">
         <v>143</v>
       </c>
       <c r="B52" s="39"/>
@@ -2586,13 +2586,13 @@
       <c r="A59" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="B59" s="57"/>
-      <c r="C59" s="57"/>
-      <c r="D59" s="57"/>
-      <c r="E59" s="57"/>
+      <c r="B59" s="53"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="52" t="s">
+      <c r="A61" s="54" t="s">
         <v>143</v>
       </c>
       <c r="B61" s="39"/>
@@ -2631,11 +2631,11 @@
       <c r="A67" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="B67" s="55" t="s">
+      <c r="B67" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="C67" s="56"/>
-      <c r="D67" s="54" t="s">
+      <c r="C67" s="52"/>
+      <c r="D67" s="57" t="s">
         <v>157</v>
       </c>
       <c r="E67" s="42"/>
@@ -2644,11 +2644,11 @@
       <c r="A68" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="B68" s="51" t="s">
+      <c r="B68" s="55" t="s">
         <v>158</v>
       </c>
       <c r="C68" s="39"/>
-      <c r="D68" s="53" t="s">
+      <c r="D68" s="56" t="s">
         <v>159</v>
       </c>
       <c r="E68" s="39"/>
@@ -2657,11 +2657,11 @@
       <c r="A69" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="B69" s="51" t="s">
+      <c r="B69" s="55" t="s">
         <v>160</v>
       </c>
       <c r="C69" s="39"/>
-      <c r="D69" s="53" t="s">
+      <c r="D69" s="56" t="s">
         <v>161</v>
       </c>
       <c r="E69" s="39"/>
@@ -2728,6 +2728,17 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="B69:C69"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="B67:C67"/>
@@ -2741,17 +2752,6 @@
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="B69:C69"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
